--- a/practice/answers/s1_q07.xlsx
+++ b/practice/answers/s1_q07.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,29 +79,19 @@
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,216 +457,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Summarising a small column</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>MIN, MAX, AVERAGE and MEDIAN over seven plots, then what happens to the mean and the median when one value moves a long way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Plot</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Yield (bu/ac)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="2" t="n">
         <v>47.2</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B3" s="2" t="n">
         <v>61.8</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B4" s="2" t="n">
         <v>39.5</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B5" s="2" t="n">
         <v>55.1</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B6" s="2" t="n">
         <v>43.7</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B7" s="2" t="n">
         <v>58.9</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B8" s="2" t="n">
         <v>50.3</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="C13" s="8">
-        <f>MIN(B5:B11)</f>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>MIN(B2:B8)</f>
         <v/>
       </c>
-      <c r="D13" s="9">
-        <f>_xlfn.FORMULATEXT(C13)</f>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>MAX</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>MAX(B2:B8)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Maximum</t>
-        </is>
-      </c>
-      <c r="C14" s="8">
-        <f>MAX(B5:B11)</f>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>AVERAGE(B2:B8)</f>
         <v/>
       </c>
-      <c r="D14" s="9">
-        <f>_xlfn.FORMULATEXT(C14)</f>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B13" s="4">
+        <f>MEDIAN(B2:B8)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="C15" s="8">
-        <f>MAX(B5:B11)-MIN(B5:B11)</f>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Range (formula)</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>MAX(B2:B8)-MIN(B2:B8)</f>
         <v/>
       </c>
-      <c r="D15" s="9">
-        <f>_xlfn.FORMULATEXT(C15)</f>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>COUNT of plots</t>
+        </is>
+      </c>
+      <c r="B15" s="8">
+        <f>COUNT(B2:B8)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="C16" s="10">
-        <f>AVERAGE(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>_xlfn.FORMULATEXT(C16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="C17" s="8">
-        <f>MEDIAN(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="9">
-        <f>_xlfn.FORMULATEXT(C17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C18" s="11">
-        <f>COUNT(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="D18" s="9">
-        <f>_xlfn.FORMULATEXT(C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1"/>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Change plot B to 91.8 and the mean climbs to 55.21 while the median stays at 50.3. The mean adds every value; the median only cares which value sits in the middle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Range (typed)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>After Plot B is changed to 91.8, the formula shows 52.3 (91.8 - 39.5) while the typed cell still reads 22.3. Both look like numbers, so a reader cannot tell which is stale -- the typed one misleads, and a sheet full of typed results does not survive its own data changing.</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:D20"/>
+  <mergeCells count="1">
+    <mergeCell ref="A18:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q07.xlsx
+++ b/practice/answers/s1_q07.xlsx
@@ -1,66 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FCAF6B54EC1656947EFBBAE0EF3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE984606-7FF7-465B-A563-E5F29AD644FA}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>Range (formula)</t>
+  </si>
+  <si>
+    <t>COUNT of plots</t>
+  </si>
+  <si>
+    <t>Range (typed)</t>
+  </si>
+  <si>
+    <t>After Plot B is changed to 91.8, the formula shows 52.3 (91.8 - 39.5) while the typed cell still reads 22.3. Both look like numbers, so a reader cannot tell which is stale -- the typed one misleads, and a sheet full of typed results does not survive its own data changing.</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,95 +165,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -452,245 +483,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
         <v>47.2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
         <v>61.8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
         <v>39.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
         <v>55.1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
         <v>43.7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
         <v>58.9</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
         <v>50.3</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
+    <row r="10" spans="1:2">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B10" s="4">
         <f>MIN(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>MAX</t>
-        </is>
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B11" s="4">
         <f>MAX(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="B12" s="5">
         <f>AVERAGE(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>MEDIAN</t>
-        </is>
+        <v>50.928571428571431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="B13" s="4">
         <f>MEDIAN(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Range (formula)</t>
-        </is>
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="B14" s="7">
         <f>MAX(B2:B8)-MIN(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>COUNT of plots</t>
-        </is>
+        <v>22.299999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="B15" s="8">
         <f>COUNT(B2:B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Range (typed)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10">
         <v>22.3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>After Plot B is changed to 91.8, the formula shows 52.3 (91.8 - 39.5) while the typed cell still reads 22.3. Both look like numbers, so a reader cannot tell which is stale -- the typed one misleads, and a sheet full of typed results does not survive its own data changing.</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/practice/answers/s1_q07.xlsx
+++ b/practice/answers/s1_q07.xlsx
@@ -1,155 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_884D7FDFD678FCAF6B54EC1656947EFBBAE0EF3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE984606-7FF7-465B-A563-E5F29AD644FA}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Plot</t>
-  </si>
-  <si>
-    <t>Yield (bu/ac)</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>AVERAGE</t>
-  </si>
-  <si>
-    <t>MEDIAN</t>
-  </si>
-  <si>
-    <t>Range (formula)</t>
-  </si>
-  <si>
-    <t>COUNT of plots</t>
-  </si>
-  <si>
-    <t>Range (typed)</t>
-  </si>
-  <si>
-    <t>After Plot B is changed to 91.8, the formula shows 52.3 (91.8 - 39.5) while the typed cell still reads 22.3. Both look like numbers, so a reader cannot tell which is stale -- the typed one misleads, and a sheet full of typed results does not survive its own data changing.</t>
-  </si>
-  <si>
-    <t>Part (a)</t>
-  </si>
-  <si>
-    <t>Part (b)</t>
-  </si>
-  <si>
-    <t>Part (c)</t>
-  </si>
-  <si>
-    <t>Part (d)</t>
-  </si>
-  <si>
-    <t>Part (e)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D2E9"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -165,37 +71,95 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -483,198 +447,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="7" width="12" customWidth="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Updated (c)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Statistic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Updated (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>47.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="C2" s="2" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F2" s="3">
+        <f>MIN(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="G2" s="4">
+        <f>MIN(C2:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>61.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="C3" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MAX</t>
+        </is>
+      </c>
+      <c r="F3" s="3">
+        <f>MAX(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="G3" s="4">
+        <f>MAX(C2:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>39.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="C4" s="2" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="F4" s="3">
+        <f>AVERAGE(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="G4" s="4">
+        <f>AVERAGE(C2:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>55.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C5" s="2" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="F5" s="3">
+        <f>MEDIAN(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="G5" s="4">
+        <f>MEDIAN(C2:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>43.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C6" s="2" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="F6" s="5">
+        <f>F3-F2</f>
+        <v/>
+      </c>
+      <c r="G6" s="4">
+        <f>G3-G2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>58.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C7" s="2" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>50.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4">
-        <f>MIN(B2:B8)</f>
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4">
-        <f>MAX(B2:B8)</f>
-        <v>61.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5">
-        <f>AVERAGE(B2:B8)</f>
-        <v>50.928571428571431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4">
-        <f>MEDIAN(B2:B8)</f>
+      <c r="C8" s="2" t="n">
         <v>50.3</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7">
-        <f>MAX(B2:B8)-MIN(B2:B8)</f>
-        <v>22.299999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8">
-        <f>COUNT(B2:B8)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="11" t="s">
-        <v>21</v>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>(c) The maximum, the mean and the range changed; the minimum and the median did not. (91.8 replaces 61.8, which was already the largest value, so the middle of the ordered list is untouched.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>(d) The median depends only on the middle of the ordered yields, and plot B stays at the top end, so the middle value never moves. The mean adds the whole 30-bushel increase and spreads it over seven plots, rising by about 4.3 bu/ac.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A18:G20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q07.xlsx
+++ b/practice/answers/s1_q07.xlsx
@@ -651,14 +651,14 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>(c) The maximum, the mean and the range changed; the minimum and the median did not. (91.8 replaces 61.8, which was already the largest value, so the middle of the ordered list is untouched.)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>(d) The median depends only on the middle of the ordered yields, and plot B stays at the top end, so the middle value never moves. The mean adds the whole 30-bushel increase and spreads it over seven plots, rising by about 4.3 bu/ac.</t>

--- a/practice/answers/s1_q07.xlsx
+++ b/practice/answers/s1_q07.xlsx
@@ -1,61 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_884D98279055966F6E1090D644A146FB8CCAF037" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Answer" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>Yield (bu/ac)</t>
+  </si>
+  <si>
+    <t>Updated (c)</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Original</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>MEDIAN</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>(c) The maximum, the mean and the range changed; the minimum and the median did not. (91.8 replaces 61.8, which was already the largest value, so the middle of the ordered list is untouched.)</t>
+  </si>
+  <si>
+    <t>(d) The median depends only on the middle of the ordered yields, and plot B stays at the top end, so the middle value never moves. The mean adds the whole 30-bushel increase and spreads it over seven plots, rising by about 4.3 bu/ac.</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,95 +166,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -447,257 +484,213 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Updated (c)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Statistic</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Updated (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <v>47.2</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>47.2</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
+      <c r="E2" t="s">
+        <v>6</v>
       </c>
       <c r="F2" s="3">
         <f>MIN(B2:B8)</f>
-        <v/>
+        <v>39.5</v>
       </c>
       <c r="G2" s="4">
         <f>MIN(C2:C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>61.8</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="2">
         <v>91.8</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MAX</t>
-        </is>
+      <c r="E3" t="s">
+        <v>8</v>
       </c>
       <c r="F3" s="3">
         <f>MAX(B2:B8)</f>
-        <v/>
+        <v>61.8</v>
       </c>
       <c r="G3" s="4">
         <f>MAX(C2:C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>39.5</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="2">
         <v>39.5</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AVERAGE</t>
-        </is>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
       <c r="F4" s="3">
         <f>AVERAGE(B2:B8)</f>
-        <v/>
+        <v>50.928571428571431</v>
       </c>
       <c r="G4" s="4">
         <f>AVERAGE(C2:C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+        <v>55.214285714285715</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
         <v>55.1</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="2">
         <v>55.1</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MEDIAN</t>
-        </is>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
       <c r="F5" s="3">
         <f>MEDIAN(B2:B8)</f>
-        <v/>
+        <v>50.3</v>
       </c>
       <c r="G5" s="4">
         <f>MEDIAN(C2:C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
         <v>43.7</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="2">
         <v>43.7</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
+      <c r="E6" t="s">
+        <v>14</v>
       </c>
       <c r="F6" s="5">
         <f>F3-F2</f>
-        <v/>
+        <v>22.299999999999997</v>
       </c>
       <c r="G6" s="4">
         <f>G3-G2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
         <v>58.9</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="2">
         <v>58.9</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
         <v>50.3</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="2">
         <v>50.3</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>(c) The maximum, the mean and the range changed; the minimum and the median did not. (91.8 replaces 61.8, which was already the largest value, so the middle of the ordered list is untouched.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>(d) The median depends only on the middle of the ordered yields, and plot B stays at the top end, so the middle value never moves. The mean adds the whole 30-bushel increase and spreads it over seven plots, rising by about 4.3 bu/ac.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
+    <row r="10" spans="1:7" ht="63.95" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="63.95" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
